--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF4327B-E25B-47B2-A1F9-29258152DB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA827B10-E881-4A82-AA32-F77783B36D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="10" xr2:uid="{661390DE-D06E-402F-B49F-05F85B2DF025}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{661390DE-D06E-402F-B49F-05F85B2DF025}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
     <sheet name="source data&gt;" sheetId="20" r:id="rId2"/>
     <sheet name="NTS 1-20" sheetId="11" r:id="rId3"/>
-    <sheet name="Table_44._Transportation_Fleet_" sheetId="23" r:id="rId4"/>
-    <sheet name="Table_45._Transportation_Fleet_" sheetId="22" r:id="rId5"/>
-    <sheet name="Table_38._Light-Duty_Vehicle_Sa" sheetId="24" r:id="rId6"/>
-    <sheet name="Table_49._Freight_Transportatio" sheetId="25" r:id="rId7"/>
+    <sheet name="AEO 2025 Table 44" sheetId="23" r:id="rId4"/>
+    <sheet name="AEO 2025 Table 45" sheetId="22" r:id="rId5"/>
+    <sheet name="AEO 2025 Table 38" sheetId="24" r:id="rId6"/>
+    <sheet name="AEO 2025 Table 49" sheetId="25" r:id="rId7"/>
     <sheet name="calcs&gt;" sheetId="21" r:id="rId8"/>
     <sheet name="Calculations" sheetId="2" r:id="rId9"/>
     <sheet name="Freight and Buses" sheetId="16" r:id="rId10"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="1106">
   <si>
     <t>Car Avg Lifetime, years (Page 22, Table 7)</t>
   </si>
@@ -3375,6 +3375,21 @@
   </si>
   <si>
     <t>Table 49.  Freight Transportation Energy Use</t>
+  </si>
+  <si>
+    <t>U.S. Energy Information Administration</t>
+  </si>
+  <si>
+    <t>Annual Energy Outlook 2025</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/outlooks/aeo/tables_side_xls.php</t>
+  </si>
+  <si>
+    <t>Scenario: Alternative Transportation</t>
+  </si>
+  <si>
+    <t>Table 44, 45, 38, 49</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3665,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3857,6 +3872,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4290,7 +4311,7 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4475,16 +4496,11 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4499,10 +4515,16 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="63">
     <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
@@ -4904,18 +4926,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B60"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="132.28515625" customWidth="1"/>
+    <col min="2" max="2" width="132.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4923,208 +4945,238 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" s="75" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" s="9">
         <v>2016</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" s="9">
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B17" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B20" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B22" s="9">
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B24" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B26" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B28" s="9">
         <v>2013</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B33" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B35" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B37" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B40" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B42" s="9">
         <v>2009</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B44" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B45" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B47" s="88" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B48" s="9">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B49" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B50" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B51" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B52" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A53" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A54" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A58" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A60" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5142,30 +5194,30 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC31426-123E-4577-A9C8-93E89562BFE4}">
   <dimension ref="A2:C21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="84">
-        <f>Table_44._Transportation_Fleet_!F66*1000</f>
+      <c r="B2" s="76">
+        <f>'AEO 2025 Table 44'!F66*1000</f>
         <v>472289.185</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="84">
-        <f>Table_45._Transportation_Fleet_!F63*1000</f>
+      <c r="B3" s="76">
+        <f>'AEO 2025 Table 45'!F63*1000</f>
         <v>14603680.663999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -5174,35 +5226,35 @@
         <v>30.921056691145701</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B5" s="37"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B6" s="37"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="84">
-        <f>SUM(Table_49._Freight_Transportatio!F255,Table_49._Freight_Transportatio!F269)*1000</f>
+      <c r="B7" s="76">
+        <f>SUM('AEO 2025 Table 49'!F255,'AEO 2025 Table 49'!F269)*1000</f>
         <v>395582.73299999995</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="84">
-        <f>SUM(Table_49._Freight_Transportatio!F166,Table_49._Freight_Transportatio!F180)*10^6</f>
+      <c r="B8" s="76">
+        <f>SUM('AEO 2025 Table 49'!F166,'AEO 2025 Table 49'!F180)*10^6</f>
         <v>9076094</v>
       </c>
       <c r="C8">
-        <f>SUM(Table_49._Freight_Transportatio!F166,Table_49._Freight_Transportatio!F180)*10^6</f>
+        <f>SUM('AEO 2025 Table 49'!F166,'AEO 2025 Table 49'!F180)*10^6</f>
         <v>9076094</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -5211,28 +5263,28 @@
         <v>22.943605073884765</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B10" s="37"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="84">
-        <f>Table_49._Freight_Transportatio!F283*1000</f>
+      <c r="B11" s="76">
+        <f>'AEO 2025 Table 49'!F283*1000</f>
         <v>313606.65899999999</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="84">
-        <f>Table_49._Freight_Transportatio!F194*10^6</f>
+      <c r="B12" s="76">
+        <f>'AEO 2025 Table 49'!F194*10^6</f>
         <v>5553924</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -5241,7 +5293,7 @@
         <v>17.709840784981548</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>158</v>
       </c>
@@ -5249,7 +5301,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -5257,7 +5309,7 @@
         <v>73000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -5266,7 +5318,7 @@
         <v>12.166666666666668</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -5274,7 +5326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -5282,7 +5334,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -5302,14 +5354,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="69" t="s">
         <v>94</v>
       </c>
@@ -5320,7 +5372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -5332,7 +5384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -5345,7 +5397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -5358,7 +5410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -5371,7 +5423,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -5384,7 +5436,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -5408,7 +5460,7 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5417,72 +5469,72 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="27" width="7.7109375" customWidth="1"/>
-    <col min="28" max="28" width="7.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.40625" customWidth="1"/>
+    <col min="2" max="27" width="7.7265625" customWidth="1"/>
+    <col min="28" max="28" width="7.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="A1" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="80"/>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
-      <c r="AA1" s="80"/>
-      <c r="AB1" s="80"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-    </row>
-    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="82"/>
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="82"/>
+      <c r="AO1" s="82"/>
+      <c r="AP1" s="82"/>
+      <c r="AQ1" s="82"/>
+      <c r="AR1" s="82"/>
+      <c r="AS1" s="82"/>
+      <c r="AT1" s="82"/>
+      <c r="AU1" s="82"/>
+      <c r="AV1" s="82"/>
+      <c r="AW1" s="82"/>
+      <c r="AX1" s="82"/>
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="82"/>
+    </row>
+    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="38"/>
       <c r="B2" s="39">
         <v>1980</v>
@@ -5592,7 +5644,7 @@
       <c r="BA2" s="45"/>
       <c r="BB2" s="46"/>
     </row>
-    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" s="47" t="s">
         <v>61</v>
       </c>
@@ -5704,7 +5756,7 @@
       <c r="BA3" s="48"/>
       <c r="BB3" s="48"/>
     </row>
-    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="50" t="s">
         <v>63</v>
       </c>
@@ -5816,7 +5868,7 @@
       <c r="BA4" s="52"/>
       <c r="BB4" s="52"/>
     </row>
-    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A5" s="50" t="s">
         <v>64</v>
       </c>
@@ -5928,7 +5980,7 @@
       <c r="BA5" s="52"/>
       <c r="BB5" s="52"/>
     </row>
-    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" s="50" t="s">
         <v>65</v>
       </c>
@@ -6040,7 +6092,7 @@
       <c r="BA6" s="52"/>
       <c r="BB6" s="52"/>
     </row>
-    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A7" s="50" t="s">
         <v>66</v>
       </c>
@@ -6152,7 +6204,7 @@
       <c r="BA7" s="52"/>
       <c r="BB7" s="52"/>
     </row>
-    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A8" s="50" t="s">
         <v>67</v>
       </c>
@@ -6264,7 +6316,7 @@
       <c r="BA8" s="52"/>
       <c r="BB8" s="52"/>
     </row>
-    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A9" s="53" t="s">
         <v>68</v>
       </c>
@@ -6322,7 +6374,7 @@
       <c r="BA9" s="54"/>
       <c r="BB9" s="54"/>
     </row>
-    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" s="50" t="s">
         <v>63</v>
       </c>
@@ -6436,7 +6488,7 @@
       <c r="BA10" s="56"/>
       <c r="BB10" s="56"/>
     </row>
-    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" s="50" t="s">
         <v>64</v>
       </c>
@@ -6548,7 +6600,7 @@
       <c r="BA11" s="56"/>
       <c r="BB11" s="56"/>
     </row>
-    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" s="50" t="s">
         <v>65</v>
       </c>
@@ -6660,7 +6712,7 @@
       <c r="BA12" s="56"/>
       <c r="BB12" s="56"/>
     </row>
-    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" s="50" t="s">
         <v>66</v>
       </c>
@@ -6772,7 +6824,7 @@
       <c r="BA13" s="56"/>
       <c r="BB13" s="56"/>
     </row>
-    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" s="50" t="s">
         <v>67</v>
       </c>
@@ -6884,7 +6936,7 @@
       <c r="BA14" s="56"/>
       <c r="BB14" s="56"/>
     </row>
-    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A15" s="47" t="s">
         <v>69</v>
       </c>
@@ -6942,7 +6994,7 @@
       <c r="BA15" s="58"/>
       <c r="BB15" s="58"/>
     </row>
-    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" s="50" t="s">
         <v>63</v>
       </c>
@@ -7054,7 +7106,7 @@
       <c r="BA16" s="59"/>
       <c r="BB16" s="59"/>
     </row>
-    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" s="50" t="s">
         <v>64</v>
       </c>
@@ -7166,7 +7218,7 @@
       <c r="BA17" s="59"/>
       <c r="BB17" s="59"/>
     </row>
-    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A18" s="50" t="s">
         <v>65</v>
       </c>
@@ -7278,7 +7330,7 @@
       <c r="BA18" s="59"/>
       <c r="BB18" s="59"/>
     </row>
-    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A19" s="50" t="s">
         <v>66</v>
       </c>
@@ -7390,7 +7442,7 @@
       <c r="BA19" s="59"/>
       <c r="BB19" s="59"/>
     </row>
-    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A20" s="60" t="s">
         <v>67</v>
       </c>
@@ -7502,233 +7554,233 @@
       <c r="BA20" s="59"/>
       <c r="BB20" s="59"/>
     </row>
-    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="82" t="s">
+    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A21" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="82"/>
-      <c r="Q21" s="82"/>
-    </row>
-    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="83"/>
-    </row>
-    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="83" t="s">
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+    </row>
+    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A22" s="84"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+    </row>
+    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A23" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-    </row>
-    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="76" t="s">
+      <c r="B23" s="84"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
+      <c r="Q23" s="84"/>
+    </row>
+    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A24" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
-      <c r="Q24" s="76"/>
-    </row>
-    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="76" t="s">
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+    </row>
+    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A25" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="76"/>
-      <c r="P25" s="76"/>
-      <c r="Q25" s="76"/>
-    </row>
-    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
+    </row>
+    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A26" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="77"/>
-      <c r="L26" s="77"/>
-      <c r="M26" s="77"/>
-      <c r="N26" s="77"/>
-      <c r="O26" s="77"/>
-      <c r="P26" s="77"/>
-      <c r="Q26" s="77"/>
-    </row>
-    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
-      <c r="M27" s="77"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="77"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-    </row>
-    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="78" t="s">
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+    </row>
+    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A27" s="85"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+    </row>
+    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A28" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-    </row>
-    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="79" t="s">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+    </row>
+    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A29" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="79"/>
-    </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="87"/>
+      <c r="N29" s="87"/>
+      <c r="O29" s="87"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="87"/>
+    </row>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.75"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.75"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AC1:BB1"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="A22:Q22"/>
     <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7737,32 +7789,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B98BD0-2AB5-48C3-A94B-802255ACBC65}">
   <dimension ref="A1:AG66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -7860,12 +7912,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>101</v>
       </c>
@@ -7873,7 +7925,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -7971,7 +8023,7 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -8069,7 +8121,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -8167,12 +8219,12 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -8270,7 +8322,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -8368,7 +8420,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -8466,7 +8518,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -8564,7 +8616,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -8662,7 +8714,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -8760,7 +8812,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -8858,7 +8910,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -8956,7 +9008,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -9054,7 +9106,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -9152,7 +9204,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -9250,7 +9302,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -9348,7 +9400,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -9446,7 +9498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -9544,7 +9596,7 @@
         <v>-3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -9642,7 +9694,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>364</v>
       </c>
@@ -9740,7 +9792,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -9838,17 +9890,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -9946,7 +9998,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -10044,7 +10096,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>124</v>
       </c>
@@ -10142,12 +10194,12 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -10245,7 +10297,7 @@
         <v>-4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -10343,7 +10395,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>232</v>
       </c>
@@ -10441,7 +10493,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>229</v>
       </c>
@@ -10539,7 +10591,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -10637,7 +10689,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -10735,7 +10787,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -10833,7 +10885,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -10931,7 +10983,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -11029,7 +11081,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -11127,7 +11179,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -11225,7 +11277,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>116</v>
       </c>
@@ -11323,7 +11375,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>117</v>
       </c>
@@ -11421,7 +11473,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -11519,7 +11571,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -11617,7 +11669,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -11715,7 +11767,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>127</v>
       </c>
@@ -11813,7 +11865,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>148</v>
       </c>
@@ -11911,12 +11963,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -12014,7 +12066,7 @@
         <v>-5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>196</v>
       </c>
@@ -12112,7 +12164,7 @@
         <v>-5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>193</v>
       </c>
@@ -12210,7 +12262,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>190</v>
       </c>
@@ -12308,7 +12360,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -12406,7 +12458,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>135</v>
       </c>
@@ -12504,7 +12556,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>182</v>
       </c>
@@ -12602,7 +12654,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -12700,7 +12752,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>139</v>
       </c>
@@ -12798,7 +12850,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>174</v>
       </c>
@@ -12896,7 +12948,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>171</v>
       </c>
@@ -12994,7 +13046,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>168</v>
       </c>
@@ -13092,7 +13144,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>291</v>
       </c>
@@ -13198,32 +13250,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6F1E4F-C2E1-4AC1-9426-39A4D1D07272}">
   <dimension ref="A1:AG63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -13321,17 +13373,17 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -13429,7 +13481,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -13527,7 +13579,7 @@
         <v>-0.123</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -13625,12 +13677,12 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -13728,7 +13780,7 @@
         <v>-0.112</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -13826,7 +13878,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -13924,7 +13976,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -14022,7 +14074,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -14120,7 +14172,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -14218,7 +14270,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -14316,7 +14368,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -14414,7 +14466,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -14512,7 +14564,7 @@
         <v>-8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -14610,7 +14662,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -14708,7 +14760,7 @@
         <v>-6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -14806,7 +14858,7 @@
         <v>-6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -14904,7 +14956,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -15002,7 +15054,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -15100,7 +15152,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>247</v>
       </c>
@@ -15198,17 +15250,17 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -15306,7 +15358,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -15404,7 +15456,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -15502,12 +15554,12 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -15605,7 +15657,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>235</v>
       </c>
@@ -15703,7 +15755,7 @@
         <v>-9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>232</v>
       </c>
@@ -15801,7 +15853,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>229</v>
       </c>
@@ -15899,7 +15951,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -15997,7 +16049,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -16095,7 +16147,7 @@
         <v>0.17599999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -16193,7 +16245,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -16291,7 +16343,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -16389,7 +16441,7 @@
         <v>-6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -16487,7 +16539,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -16585,7 +16637,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -16683,7 +16735,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -16781,7 +16833,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -16879,7 +16931,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>126</v>
       </c>
@@ -16977,7 +17029,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>204</v>
       </c>
@@ -17075,7 +17127,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>148</v>
       </c>
@@ -17173,7 +17225,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>199</v>
       </c>
@@ -17271,7 +17323,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>196</v>
       </c>
@@ -17369,7 +17421,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>193</v>
       </c>
@@ -17467,7 +17519,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>190</v>
       </c>
@@ -17565,7 +17617,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>187</v>
       </c>
@@ -17663,7 +17715,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>135</v>
       </c>
@@ -17761,7 +17813,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -17859,7 +17911,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>179</v>
       </c>
@@ -17957,7 +18009,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>139</v>
       </c>
@@ -18055,7 +18107,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>174</v>
       </c>
@@ -18153,7 +18205,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>171</v>
       </c>
@@ -18251,7 +18303,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>168</v>
       </c>
@@ -18349,7 +18401,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>165</v>
       </c>
@@ -18455,29 +18507,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D130767C-6285-4C0E-BDF9-7A9F61BDC9F4}">
   <dimension ref="A1:AG67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -18575,17 +18627,17 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -18683,7 +18735,7 @@
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -18781,7 +18833,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -18879,12 +18931,12 @@
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -18982,7 +19034,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -19080,7 +19132,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -19178,7 +19230,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -19276,7 +19328,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -19374,7 +19426,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -19472,7 +19524,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -19570,7 +19622,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -19668,7 +19720,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -19766,7 +19818,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -19864,7 +19916,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -19962,7 +20014,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -20060,7 +20112,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -20158,7 +20210,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -20256,7 +20308,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -20354,7 +20406,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>364</v>
       </c>
@@ -20452,7 +20504,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -20550,17 +20602,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -20658,7 +20710,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -20756,7 +20808,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>124</v>
       </c>
@@ -20854,12 +20906,12 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -20957,7 +21009,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -21055,7 +21107,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>232</v>
       </c>
@@ -21153,7 +21205,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>229</v>
       </c>
@@ -21251,7 +21303,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -21349,7 +21401,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -21447,7 +21499,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -21545,7 +21597,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -21643,7 +21695,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -21741,7 +21793,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -21839,7 +21891,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -21937,7 +21989,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>116</v>
       </c>
@@ -22035,7 +22087,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>117</v>
       </c>
@@ -22133,7 +22185,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -22231,7 +22283,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -22329,7 +22381,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -22427,7 +22479,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>127</v>
       </c>
@@ -22525,7 +22577,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -22623,7 +22675,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -22721,7 +22773,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>129</v>
       </c>
@@ -22819,7 +22871,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>130</v>
       </c>
@@ -22827,7 +22879,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>132</v>
       </c>
@@ -22925,7 +22977,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>133</v>
       </c>
@@ -23023,7 +23075,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>134</v>
       </c>
@@ -23121,7 +23173,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>135</v>
       </c>
@@ -23219,7 +23271,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -23317,7 +23369,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>137</v>
       </c>
@@ -23415,7 +23467,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>138</v>
       </c>
@@ -23513,7 +23565,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -23611,7 +23663,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>140</v>
       </c>
@@ -23709,7 +23761,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>141</v>
       </c>
@@ -23807,7 +23859,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -23905,7 +23957,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -24011,33 +24063,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00A17A9-9291-44B9-93C2-28F7BD4C132B}">
   <dimension ref="A1:AG309"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.26953125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -24135,22 +24187,22 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>196</v>
       </c>
@@ -24248,7 +24300,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>199</v>
       </c>
@@ -24346,7 +24398,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>193</v>
       </c>
@@ -24444,7 +24496,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>190</v>
       </c>
@@ -24542,7 +24594,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>187</v>
       </c>
@@ -24640,7 +24692,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>135</v>
       </c>
@@ -24738,7 +24790,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -24836,7 +24888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -24934,7 +24986,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>139</v>
       </c>
@@ -25032,7 +25084,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>174</v>
       </c>
@@ -25130,7 +25182,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -25228,7 +25280,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -25326,110 +25378,110 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="85" t="s">
+    <row r="21" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A21" s="77" t="s">
         <v>628</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="77" t="s">
         <v>1071</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="77" t="s">
         <v>1070</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="77" t="s">
         <v>1014</v>
       </c>
-      <c r="F21" s="85">
+      <c r="F21" s="77">
         <v>81.913414000000003</v>
       </c>
-      <c r="G21" s="85">
+      <c r="G21" s="77">
         <v>83.637932000000006</v>
       </c>
-      <c r="H21" s="85">
+      <c r="H21" s="77">
         <v>84.649970999999994</v>
       </c>
-      <c r="I21" s="85">
+      <c r="I21" s="77">
         <v>85.366112000000001</v>
       </c>
-      <c r="J21" s="85">
+      <c r="J21" s="77">
         <v>86.041008000000005</v>
       </c>
-      <c r="K21" s="85">
+      <c r="K21" s="77">
         <v>87.189673999999997</v>
       </c>
-      <c r="L21" s="85">
+      <c r="L21" s="77">
         <v>88.634345999999994</v>
       </c>
-      <c r="M21" s="85">
+      <c r="M21" s="77">
         <v>90.136009000000001</v>
       </c>
-      <c r="N21" s="85">
+      <c r="N21" s="77">
         <v>91.764342999999997</v>
       </c>
-      <c r="O21" s="85">
+      <c r="O21" s="77">
         <v>93.408591999999999</v>
       </c>
-      <c r="P21" s="85">
+      <c r="P21" s="77">
         <v>95.227249</v>
       </c>
-      <c r="Q21" s="85">
+      <c r="Q21" s="77">
         <v>97.079216000000002</v>
       </c>
-      <c r="R21" s="85">
+      <c r="R21" s="77">
         <v>99.016814999999994</v>
       </c>
-      <c r="S21" s="85">
+      <c r="S21" s="77">
         <v>100.936539</v>
       </c>
-      <c r="T21" s="85">
+      <c r="T21" s="77">
         <v>102.872658</v>
       </c>
-      <c r="U21" s="85">
+      <c r="U21" s="77">
         <v>104.776962</v>
       </c>
-      <c r="V21" s="85">
+      <c r="V21" s="77">
         <v>106.826088</v>
       </c>
-      <c r="W21" s="85">
+      <c r="W21" s="77">
         <v>108.78827699999999</v>
       </c>
-      <c r="X21" s="85">
+      <c r="X21" s="77">
         <v>110.690437</v>
       </c>
-      <c r="Y21" s="85">
+      <c r="Y21" s="77">
         <v>112.395782</v>
       </c>
-      <c r="Z21" s="85">
+      <c r="Z21" s="77">
         <v>114.059608</v>
       </c>
-      <c r="AA21" s="85">
+      <c r="AA21" s="77">
         <v>115.924751</v>
       </c>
-      <c r="AB21" s="85">
+      <c r="AB21" s="77">
         <v>117.859016</v>
       </c>
-      <c r="AC21" s="85">
+      <c r="AC21" s="77">
         <v>120.16201</v>
       </c>
-      <c r="AD21" s="85">
+      <c r="AD21" s="77">
         <v>122.30836499999999</v>
       </c>
-      <c r="AE21" s="85">
+      <c r="AE21" s="77">
         <v>124.313187</v>
       </c>
-      <c r="AF21" s="85">
+      <c r="AF21" s="77">
         <v>126.225555</v>
       </c>
-      <c r="AG21" s="86">
+      <c r="AG21" s="78">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>196</v>
       </c>
@@ -25527,7 +25579,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -25625,7 +25677,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>193</v>
       </c>
@@ -25723,7 +25775,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -25821,7 +25873,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>187</v>
       </c>
@@ -25919,7 +25971,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -26017,7 +26069,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>179</v>
       </c>
@@ -26115,7 +26167,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -26213,7 +26265,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -26311,7 +26363,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -26409,7 +26461,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>171</v>
       </c>
@@ -26507,7 +26559,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>168</v>
       </c>
@@ -26605,110 +26657,110 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="85" t="s">
+    <row r="35" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A35" s="77" t="s">
         <v>600</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="77" t="s">
         <v>1045</v>
       </c>
-      <c r="C35" s="85" t="s">
+      <c r="C35" s="77" t="s">
         <v>1044</v>
       </c>
-      <c r="D35" s="85" t="s">
+      <c r="D35" s="77" t="s">
         <v>1014</v>
       </c>
-      <c r="F35" s="85">
+      <c r="F35" s="77">
         <v>62.669761999999999</v>
       </c>
-      <c r="G35" s="85">
+      <c r="G35" s="77">
         <v>62.306469</v>
       </c>
-      <c r="H35" s="85">
+      <c r="H35" s="77">
         <v>61.636169000000002</v>
       </c>
-      <c r="I35" s="85">
+      <c r="I35" s="77">
         <v>61.069248000000002</v>
       </c>
-      <c r="J35" s="85">
+      <c r="J35" s="77">
         <v>60.511715000000002</v>
       </c>
-      <c r="K35" s="85">
+      <c r="K35" s="77">
         <v>60.140095000000002</v>
       </c>
-      <c r="L35" s="85">
+      <c r="L35" s="77">
         <v>59.894455000000001</v>
       </c>
-      <c r="M35" s="85">
+      <c r="M35" s="77">
         <v>59.670211999999999</v>
       </c>
-      <c r="N35" s="85">
+      <c r="N35" s="77">
         <v>59.550327000000003</v>
       </c>
-      <c r="O35" s="85">
+      <c r="O35" s="77">
         <v>59.398045000000003</v>
       </c>
-      <c r="P35" s="85">
+      <c r="P35" s="77">
         <v>59.327106000000001</v>
       </c>
-      <c r="Q35" s="85">
+      <c r="Q35" s="77">
         <v>59.290576999999999</v>
       </c>
-      <c r="R35" s="85">
+      <c r="R35" s="77">
         <v>59.361587999999998</v>
       </c>
-      <c r="S35" s="85">
+      <c r="S35" s="77">
         <v>59.521720999999999</v>
       </c>
-      <c r="T35" s="85">
+      <c r="T35" s="77">
         <v>59.692307</v>
       </c>
-      <c r="U35" s="85">
+      <c r="U35" s="77">
         <v>59.831532000000003</v>
       </c>
-      <c r="V35" s="85">
+      <c r="V35" s="77">
         <v>60.013888999999999</v>
       </c>
-      <c r="W35" s="85">
+      <c r="W35" s="77">
         <v>60.179622999999999</v>
       </c>
-      <c r="X35" s="85">
+      <c r="X35" s="77">
         <v>60.380524000000001</v>
       </c>
-      <c r="Y35" s="85">
+      <c r="Y35" s="77">
         <v>60.561053999999999</v>
       </c>
-      <c r="Z35" s="85">
+      <c r="Z35" s="77">
         <v>60.717669999999998</v>
       </c>
-      <c r="AA35" s="85">
+      <c r="AA35" s="77">
         <v>60.904583000000002</v>
       </c>
-      <c r="AB35" s="85">
+      <c r="AB35" s="77">
         <v>61.056731999999997</v>
       </c>
-      <c r="AC35" s="85">
+      <c r="AC35" s="77">
         <v>61.433689000000001</v>
       </c>
-      <c r="AD35" s="85">
+      <c r="AD35" s="77">
         <v>61.823250000000002</v>
       </c>
-      <c r="AE35" s="85">
+      <c r="AE35" s="77">
         <v>62.164485999999997</v>
       </c>
-      <c r="AF35" s="85">
+      <c r="AF35" s="77">
         <v>62.394100000000002</v>
       </c>
-      <c r="AG35" s="86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG35" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>196</v>
       </c>
@@ -26806,7 +26858,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>199</v>
       </c>
@@ -26904,7 +26956,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>193</v>
       </c>
@@ -27002,7 +27054,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -27100,7 +27152,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>187</v>
       </c>
@@ -27198,7 +27250,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -27296,7 +27348,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>179</v>
       </c>
@@ -27394,7 +27446,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>182</v>
       </c>
@@ -27492,7 +27544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>139</v>
       </c>
@@ -27590,7 +27642,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>174</v>
       </c>
@@ -27688,7 +27740,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>171</v>
       </c>
@@ -27786,7 +27838,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>168</v>
       </c>
@@ -27884,7 +27936,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>572</v>
       </c>
@@ -27982,7 +28034,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>1017</v>
       </c>
@@ -28080,17 +28132,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>196</v>
       </c>
@@ -28188,7 +28240,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -28286,7 +28338,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>193</v>
       </c>
@@ -28384,7 +28436,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>190</v>
       </c>
@@ -28482,7 +28534,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>187</v>
       </c>
@@ -28580,7 +28632,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>135</v>
       </c>
@@ -28678,7 +28730,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>179</v>
       </c>
@@ -28776,7 +28828,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>182</v>
       </c>
@@ -28874,7 +28926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>139</v>
       </c>
@@ -28972,7 +29024,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -29070,7 +29122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>171</v>
       </c>
@@ -29168,7 +29220,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>168</v>
       </c>
@@ -29266,7 +29318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>628</v>
       </c>
@@ -29364,12 +29416,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>196</v>
       </c>
@@ -29467,7 +29519,7 @@
         <v>-2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -29565,7 +29617,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -29663,7 +29715,7 @@
         <v>-0.104</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -29761,7 +29813,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>187</v>
       </c>
@@ -29859,7 +29911,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>135</v>
       </c>
@@ -29957,7 +30009,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>179</v>
       </c>
@@ -30055,7 +30107,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>182</v>
       </c>
@@ -30153,7 +30205,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>139</v>
       </c>
@@ -30251,7 +30303,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>174</v>
       </c>
@@ -30349,7 +30401,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -30447,7 +30499,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>168</v>
       </c>
@@ -30545,7 +30597,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>600</v>
       </c>
@@ -30643,12 +30695,12 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>196</v>
       </c>
@@ -30746,7 +30798,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>199</v>
       </c>
@@ -30844,7 +30896,7 @@
         <v>-5.5E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>193</v>
       </c>
@@ -30942,7 +30994,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>190</v>
       </c>
@@ -31040,7 +31092,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>187</v>
       </c>
@@ -31138,7 +31190,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>135</v>
       </c>
@@ -31236,7 +31288,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>179</v>
       </c>
@@ -31334,7 +31386,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>182</v>
       </c>
@@ -31432,7 +31484,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>139</v>
       </c>
@@ -31530,7 +31582,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>174</v>
       </c>
@@ -31628,7 +31680,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>171</v>
       </c>
@@ -31726,7 +31778,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>168</v>
       </c>
@@ -31824,7 +31876,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>572</v>
       </c>
@@ -31922,7 +31974,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>653</v>
       </c>
@@ -31933,7 +31985,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>196</v>
       </c>
@@ -32031,7 +32083,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>199</v>
       </c>
@@ -32129,7 +32181,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -32227,7 +32279,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>190</v>
       </c>
@@ -32325,7 +32377,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A99" t="s">
         <v>187</v>
       </c>
@@ -32423,7 +32475,7 @@
         <v>-0.109</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -32521,7 +32573,7 @@
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A101" t="s">
         <v>179</v>
       </c>
@@ -32619,7 +32671,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A102" t="s">
         <v>182</v>
       </c>
@@ -32717,7 +32769,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A103" t="s">
         <v>139</v>
       </c>
@@ -32815,7 +32867,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A104" t="s">
         <v>174</v>
       </c>
@@ -32913,7 +32965,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A105" t="s">
         <v>171</v>
       </c>
@@ -33011,7 +33063,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>168</v>
       </c>
@@ -33109,7 +33161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>908</v>
       </c>
@@ -33207,17 +33259,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>196</v>
       </c>
@@ -33315,7 +33367,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>199</v>
       </c>
@@ -33413,7 +33465,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>193</v>
       </c>
@@ -33511,7 +33563,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>190</v>
       </c>
@@ -33609,7 +33661,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A114" t="s">
         <v>187</v>
       </c>
@@ -33707,7 +33759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>135</v>
       </c>
@@ -33805,7 +33857,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>179</v>
       </c>
@@ -33903,7 +33955,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>182</v>
       </c>
@@ -34001,7 +34053,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -34099,7 +34151,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A119" t="s">
         <v>174</v>
       </c>
@@ -34197,7 +34249,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A120" t="s">
         <v>171</v>
       </c>
@@ -34295,7 +34347,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>168</v>
       </c>
@@ -34393,7 +34445,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>717</v>
       </c>
@@ -34488,12 +34540,12 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>196</v>
       </c>
@@ -34591,7 +34643,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>199</v>
       </c>
@@ -34689,7 +34741,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>193</v>
       </c>
@@ -34787,7 +34839,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>190</v>
       </c>
@@ -34885,7 +34937,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>187</v>
       </c>
@@ -34983,7 +35035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A129" t="s">
         <v>135</v>
       </c>
@@ -35081,7 +35133,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>179</v>
       </c>
@@ -35179,7 +35231,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>182</v>
       </c>
@@ -35277,7 +35329,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -35375,7 +35427,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>174</v>
       </c>
@@ -35473,7 +35525,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A134" t="s">
         <v>171</v>
       </c>
@@ -35571,7 +35623,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -35669,7 +35721,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A136" t="s">
         <v>689</v>
       </c>
@@ -35764,12 +35816,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A137" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>196</v>
       </c>
@@ -35867,7 +35919,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>199</v>
       </c>
@@ -35965,7 +36017,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>193</v>
       </c>
@@ -36063,7 +36115,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>190</v>
       </c>
@@ -36161,7 +36213,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>187</v>
       </c>
@@ -36259,7 +36311,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>135</v>
       </c>
@@ -36357,7 +36409,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -36455,7 +36507,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A145" t="s">
         <v>182</v>
       </c>
@@ -36553,7 +36605,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -36651,7 +36703,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -36749,7 +36801,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>171</v>
       </c>
@@ -36847,7 +36899,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -36945,7 +36997,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A150" t="s">
         <v>660</v>
       </c>
@@ -37040,7 +37092,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A151" t="s">
         <v>657</v>
       </c>
@@ -37135,17 +37187,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A152" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A153" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A154" t="s">
         <v>196</v>
       </c>
@@ -37243,7 +37295,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -37341,7 +37393,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A156" t="s">
         <v>193</v>
       </c>
@@ -37439,7 +37491,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -37537,7 +37589,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A158" t="s">
         <v>187</v>
       </c>
@@ -37635,7 +37687,7 @@
         <v>-6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A159" t="s">
         <v>135</v>
       </c>
@@ -37733,7 +37785,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A160" t="s">
         <v>179</v>
       </c>
@@ -37831,7 +37883,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A161" t="s">
         <v>182</v>
       </c>
@@ -37929,7 +37981,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -38027,7 +38079,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A163" t="s">
         <v>174</v>
       </c>
@@ -38125,7 +38177,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -38223,7 +38275,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -38321,7 +38373,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="166" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A166" s="1" t="s">
         <v>628</v>
       </c>
@@ -38415,16 +38467,16 @@
       <c r="AF166" s="1">
         <v>9.5095489999999998</v>
       </c>
-      <c r="AG166" s="87">
+      <c r="AG166" s="79">
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A167" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A168" t="s">
         <v>196</v>
       </c>
@@ -38522,7 +38574,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -38620,7 +38672,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A170" t="s">
         <v>193</v>
       </c>
@@ -38718,7 +38770,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -38816,7 +38868,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A172" t="s">
         <v>187</v>
       </c>
@@ -38914,7 +38966,7 @@
         <v>-5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A173" t="s">
         <v>135</v>
       </c>
@@ -39012,7 +39064,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A174" t="s">
         <v>179</v>
       </c>
@@ -39110,7 +39162,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -39208,7 +39260,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A176" t="s">
         <v>139</v>
       </c>
@@ -39306,7 +39358,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A177" t="s">
         <v>174</v>
       </c>
@@ -39404,7 +39456,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A178" t="s">
         <v>171</v>
       </c>
@@ -39502,7 +39554,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A179" t="s">
         <v>168</v>
       </c>
@@ -39600,7 +39652,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="180" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A180" s="1" t="s">
         <v>600</v>
       </c>
@@ -39694,16 +39746,16 @@
       <c r="AF180" s="1">
         <v>4.6110850000000001</v>
       </c>
-      <c r="AG180" s="87">
+      <c r="AG180" s="79">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A181" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -39801,7 +39853,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -39899,7 +39951,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A184" t="s">
         <v>193</v>
       </c>
@@ -39997,7 +40049,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -40095,7 +40147,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A186" t="s">
         <v>187</v>
       </c>
@@ -40193,7 +40245,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A187" t="s">
         <v>135</v>
       </c>
@@ -40291,7 +40343,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A188" t="s">
         <v>179</v>
       </c>
@@ -40389,7 +40441,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A189" t="s">
         <v>182</v>
       </c>
@@ -40487,7 +40539,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A190" t="s">
         <v>139</v>
       </c>
@@ -40585,7 +40637,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A191" t="s">
         <v>174</v>
       </c>
@@ -40683,7 +40735,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A192" t="s">
         <v>171</v>
       </c>
@@ -40781,7 +40833,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A193" t="s">
         <v>168</v>
       </c>
@@ -40879,105 +40931,105 @@
         <v>111</v>
       </c>
     </row>
-    <row r="194" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="85" t="s">
+    <row r="194" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A194" s="77" t="s">
         <v>572</v>
       </c>
-      <c r="B194" s="85" t="s">
+      <c r="B194" s="77" t="s">
         <v>748</v>
       </c>
-      <c r="C194" s="85" t="s">
+      <c r="C194" s="77" t="s">
         <v>747</v>
       </c>
-      <c r="D194" s="85" t="s">
+      <c r="D194" s="77" t="s">
         <v>743</v>
       </c>
-      <c r="F194" s="85">
+      <c r="F194" s="77">
         <v>5.5539240000000003</v>
       </c>
-      <c r="G194" s="85">
+      <c r="G194" s="77">
         <v>5.6442329999999998</v>
       </c>
-      <c r="H194" s="85">
+      <c r="H194" s="77">
         <v>5.7684139999999999</v>
       </c>
-      <c r="I194" s="85">
+      <c r="I194" s="77">
         <v>5.9133979999999999</v>
       </c>
-      <c r="J194" s="85">
+      <c r="J194" s="77">
         <v>6.0484790000000004</v>
       </c>
-      <c r="K194" s="85">
+      <c r="K194" s="77">
         <v>6.1621829999999997</v>
       </c>
-      <c r="L194" s="85">
+      <c r="L194" s="77">
         <v>6.2651370000000002</v>
       </c>
-      <c r="M194" s="85">
+      <c r="M194" s="77">
         <v>6.3581779999999997</v>
       </c>
-      <c r="N194" s="85">
+      <c r="N194" s="77">
         <v>6.4425569999999999</v>
       </c>
-      <c r="O194" s="85">
+      <c r="O194" s="77">
         <v>6.5187679999999997</v>
       </c>
-      <c r="P194" s="85">
+      <c r="P194" s="77">
         <v>6.5823070000000001</v>
       </c>
-      <c r="Q194" s="85">
+      <c r="Q194" s="77">
         <v>6.6453530000000001</v>
       </c>
-      <c r="R194" s="85">
+      <c r="R194" s="77">
         <v>6.7149859999999997</v>
       </c>
-      <c r="S194" s="85">
+      <c r="S194" s="77">
         <v>6.7869659999999996</v>
       </c>
-      <c r="T194" s="85">
+      <c r="T194" s="77">
         <v>6.8584779999999999</v>
       </c>
-      <c r="U194" s="85">
+      <c r="U194" s="77">
         <v>6.9200189999999999</v>
       </c>
-      <c r="V194" s="85">
+      <c r="V194" s="77">
         <v>6.9721710000000003</v>
       </c>
-      <c r="W194" s="85">
+      <c r="W194" s="77">
         <v>7.01058</v>
       </c>
-      <c r="X194" s="85">
+      <c r="X194" s="77">
         <v>7.0601390000000004</v>
       </c>
-      <c r="Y194" s="85">
+      <c r="Y194" s="77">
         <v>7.1162190000000001</v>
       </c>
-      <c r="Z194" s="85">
+      <c r="Z194" s="77">
         <v>7.1760700000000002</v>
       </c>
-      <c r="AA194" s="85">
+      <c r="AA194" s="77">
         <v>7.2330199999999998</v>
       </c>
-      <c r="AB194" s="85">
+      <c r="AB194" s="77">
         <v>7.2788839999999997</v>
       </c>
-      <c r="AC194" s="85">
+      <c r="AC194" s="77">
         <v>7.3200570000000003</v>
       </c>
-      <c r="AD194" s="85">
+      <c r="AD194" s="77">
         <v>7.3594530000000002</v>
       </c>
-      <c r="AE194" s="85">
+      <c r="AE194" s="77">
         <v>7.390244</v>
       </c>
-      <c r="AF194" s="85">
+      <c r="AF194" s="77">
         <v>7.408112</v>
       </c>
-      <c r="AG194" s="86">
+      <c r="AG194" s="78">
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A195" t="s">
         <v>746</v>
       </c>
@@ -41075,22 +41127,22 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A196" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A197" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A198" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A199" t="s">
         <v>196</v>
       </c>
@@ -41188,7 +41240,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -41286,7 +41338,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A201" t="s">
         <v>193</v>
       </c>
@@ -41384,7 +41436,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A202" t="s">
         <v>190</v>
       </c>
@@ -41482,7 +41534,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A203" t="s">
         <v>187</v>
       </c>
@@ -41580,7 +41632,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A204" t="s">
         <v>135</v>
       </c>
@@ -41678,7 +41730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A205" t="s">
         <v>179</v>
       </c>
@@ -41776,7 +41828,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A206" t="s">
         <v>182</v>
       </c>
@@ -41874,7 +41926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A207" t="s">
         <v>139</v>
       </c>
@@ -41972,7 +42024,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A208" t="s">
         <v>174</v>
       </c>
@@ -42070,7 +42122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A209" t="s">
         <v>171</v>
       </c>
@@ -42168,7 +42220,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A210" t="s">
         <v>168</v>
       </c>
@@ -42266,7 +42318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A211" t="s">
         <v>717</v>
       </c>
@@ -42361,12 +42413,12 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A212" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A213" t="s">
         <v>196</v>
       </c>
@@ -42464,7 +42516,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -42562,7 +42614,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A215" t="s">
         <v>193</v>
       </c>
@@ -42660,7 +42712,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -42758,7 +42810,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A217" t="s">
         <v>187</v>
       </c>
@@ -42856,7 +42908,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A218" t="s">
         <v>135</v>
       </c>
@@ -42954,7 +43006,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A219" t="s">
         <v>179</v>
       </c>
@@ -43052,7 +43104,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A220" t="s">
         <v>182</v>
       </c>
@@ -43150,7 +43202,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A221" t="s">
         <v>139</v>
       </c>
@@ -43248,7 +43300,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A222" t="s">
         <v>174</v>
       </c>
@@ -43346,7 +43398,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A223" t="s">
         <v>171</v>
       </c>
@@ -43444,7 +43496,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A224" t="s">
         <v>168</v>
       </c>
@@ -43542,7 +43594,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A225" t="s">
         <v>689</v>
       </c>
@@ -43637,12 +43689,12 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A226" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -43740,7 +43792,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A228" t="s">
         <v>199</v>
       </c>
@@ -43838,7 +43890,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A229" t="s">
         <v>193</v>
       </c>
@@ -43936,7 +43988,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -44034,7 +44086,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A231" t="s">
         <v>187</v>
       </c>
@@ -44132,7 +44184,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="232" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A232" t="s">
         <v>135</v>
       </c>
@@ -44230,7 +44282,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A233" t="s">
         <v>179</v>
       </c>
@@ -44328,7 +44380,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A234" t="s">
         <v>182</v>
       </c>
@@ -44426,7 +44478,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A235" t="s">
         <v>139</v>
       </c>
@@ -44524,7 +44576,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A236" t="s">
         <v>174</v>
       </c>
@@ -44622,7 +44674,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A237" t="s">
         <v>171</v>
       </c>
@@ -44720,7 +44772,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A238" t="s">
         <v>168</v>
       </c>
@@ -44818,7 +44870,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A239" t="s">
         <v>660</v>
       </c>
@@ -44913,7 +44965,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A240" t="s">
         <v>657</v>
       </c>
@@ -45008,17 +45060,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A241" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A242" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A243" t="s">
         <v>196</v>
       </c>
@@ -45116,7 +45168,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A244" t="s">
         <v>199</v>
       </c>
@@ -45214,7 +45266,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A245" t="s">
         <v>193</v>
       </c>
@@ -45312,7 +45364,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A246" t="s">
         <v>190</v>
       </c>
@@ -45410,7 +45462,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A247" t="s">
         <v>187</v>
       </c>
@@ -45508,7 +45560,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A248" t="s">
         <v>135</v>
       </c>
@@ -45606,7 +45658,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A249" t="s">
         <v>179</v>
       </c>
@@ -45704,7 +45756,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A250" t="s">
         <v>182</v>
       </c>
@@ -45802,7 +45854,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A251" t="s">
         <v>139</v>
       </c>
@@ -45900,7 +45952,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A252" t="s">
         <v>174</v>
       </c>
@@ -45998,7 +46050,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A253" t="s">
         <v>171</v>
       </c>
@@ -46096,7 +46148,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A254" t="s">
         <v>168</v>
       </c>
@@ -46194,110 +46246,110 @@
         <v>111</v>
       </c>
     </row>
-    <row r="255" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="85" t="s">
+    <row r="255" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A255" s="77" t="s">
         <v>628</v>
       </c>
-      <c r="B255" s="85" t="s">
+      <c r="B255" s="77" t="s">
         <v>627</v>
       </c>
-      <c r="C255" s="85" t="s">
+      <c r="C255" s="77" t="s">
         <v>626</v>
       </c>
-      <c r="D255" s="85" t="s">
+      <c r="D255" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F255" s="85">
+      <c r="F255" s="77">
         <v>218.36299099999999</v>
       </c>
-      <c r="G255" s="85">
+      <c r="G255" s="77">
         <v>315.76449600000001</v>
       </c>
-      <c r="H255" s="85">
+      <c r="H255" s="77">
         <v>331.76449600000001</v>
       </c>
-      <c r="I255" s="85">
+      <c r="I255" s="77">
         <v>338.70901500000002</v>
       </c>
-      <c r="J255" s="85">
+      <c r="J255" s="77">
         <v>333.87792999999999</v>
       </c>
-      <c r="K255" s="85">
+      <c r="K255" s="77">
         <v>331.958191</v>
       </c>
-      <c r="L255" s="85">
+      <c r="L255" s="77">
         <v>331.47467</v>
       </c>
-      <c r="M255" s="85">
+      <c r="M255" s="77">
         <v>328.36953699999998</v>
       </c>
-      <c r="N255" s="85">
+      <c r="N255" s="77">
         <v>329.76156600000002</v>
       </c>
-      <c r="O255" s="85">
+      <c r="O255" s="77">
         <v>335.15133700000001</v>
       </c>
-      <c r="P255" s="85">
+      <c r="P255" s="77">
         <v>340.68307499999997</v>
       </c>
-      <c r="Q255" s="85">
+      <c r="Q255" s="77">
         <v>344.650757</v>
       </c>
-      <c r="R255" s="85">
+      <c r="R255" s="77">
         <v>348.52252199999998</v>
       </c>
-      <c r="S255" s="85">
+      <c r="S255" s="77">
         <v>352.58496100000002</v>
       </c>
-      <c r="T255" s="85">
+      <c r="T255" s="77">
         <v>357.61010700000003</v>
       </c>
-      <c r="U255" s="85">
+      <c r="U255" s="77">
         <v>363.27615400000002</v>
       </c>
-      <c r="V255" s="85">
+      <c r="V255" s="77">
         <v>367.84466600000002</v>
       </c>
-      <c r="W255" s="85">
+      <c r="W255" s="77">
         <v>370.84301799999997</v>
       </c>
-      <c r="X255" s="85">
+      <c r="X255" s="77">
         <v>373.680725</v>
       </c>
-      <c r="Y255" s="85">
+      <c r="Y255" s="77">
         <v>375.94732699999997</v>
       </c>
-      <c r="Z255" s="85">
+      <c r="Z255" s="77">
         <v>378.958191</v>
       </c>
-      <c r="AA255" s="85">
+      <c r="AA255" s="77">
         <v>382.14627100000001</v>
       </c>
-      <c r="AB255" s="85">
+      <c r="AB255" s="77">
         <v>384.421967</v>
       </c>
-      <c r="AC255" s="85">
+      <c r="AC255" s="77">
         <v>386.62838699999998</v>
       </c>
-      <c r="AD255" s="85">
+      <c r="AD255" s="77">
         <v>387.21048000000002</v>
       </c>
-      <c r="AE255" s="85">
+      <c r="AE255" s="77">
         <v>388.30838</v>
       </c>
-      <c r="AF255" s="85">
+      <c r="AF255" s="77">
         <v>390.23971599999999</v>
       </c>
-      <c r="AG255" s="86">
+      <c r="AG255" s="78">
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A256" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="257" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A257" t="s">
         <v>196</v>
       </c>
@@ -46395,7 +46447,7 @@
         <v>-2.3E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A258" t="s">
         <v>199</v>
       </c>
@@ -46493,7 +46545,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A259" t="s">
         <v>193</v>
       </c>
@@ -46591,7 +46643,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A260" t="s">
         <v>190</v>
       </c>
@@ -46689,7 +46741,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A261" t="s">
         <v>187</v>
       </c>
@@ -46787,7 +46839,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A262" t="s">
         <v>135</v>
       </c>
@@ -46885,7 +46937,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A263" t="s">
         <v>179</v>
       </c>
@@ -46983,7 +47035,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A264" t="s">
         <v>182</v>
       </c>
@@ -47081,7 +47133,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="265" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A265" t="s">
         <v>139</v>
       </c>
@@ -47179,7 +47231,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="266" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A266" t="s">
         <v>174</v>
       </c>
@@ -47277,7 +47329,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="267" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A267" t="s">
         <v>171</v>
       </c>
@@ -47375,7 +47427,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="268" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A268" t="s">
         <v>168</v>
       </c>
@@ -47473,110 +47525,110 @@
         <v>111</v>
       </c>
     </row>
-    <row r="269" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="85" t="s">
+    <row r="269" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A269" s="77" t="s">
         <v>600</v>
       </c>
-      <c r="B269" s="85" t="s">
+      <c r="B269" s="77" t="s">
         <v>599</v>
       </c>
-      <c r="C269" s="85" t="s">
+      <c r="C269" s="77" t="s">
         <v>598</v>
       </c>
-      <c r="D269" s="85" t="s">
+      <c r="D269" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F269" s="85">
+      <c r="F269" s="77">
         <v>177.219742</v>
       </c>
-      <c r="G269" s="85">
+      <c r="G269" s="77">
         <v>180.500732</v>
       </c>
-      <c r="H269" s="85">
+      <c r="H269" s="77">
         <v>193.36677599999999</v>
       </c>
-      <c r="I269" s="85">
+      <c r="I269" s="77">
         <v>202.658447</v>
       </c>
-      <c r="J269" s="85">
+      <c r="J269" s="77">
         <v>197.48968500000001</v>
       </c>
-      <c r="K269" s="85">
+      <c r="K269" s="77">
         <v>188.96127300000001</v>
       </c>
-      <c r="L269" s="85">
+      <c r="L269" s="77">
         <v>183.93614199999999</v>
       </c>
-      <c r="M269" s="85">
+      <c r="M269" s="77">
         <v>179.28994800000001</v>
       </c>
-      <c r="N269" s="85">
+      <c r="N269" s="77">
         <v>177.31608600000001</v>
       </c>
-      <c r="O269" s="85">
+      <c r="O269" s="77">
         <v>177.85307299999999</v>
       </c>
-      <c r="P269" s="85">
+      <c r="P269" s="77">
         <v>177.42384300000001</v>
       </c>
-      <c r="Q269" s="85">
+      <c r="Q269" s="77">
         <v>176.68826300000001</v>
       </c>
-      <c r="R269" s="85">
+      <c r="R269" s="77">
         <v>177.73182700000001</v>
       </c>
-      <c r="S269" s="85">
+      <c r="S269" s="77">
         <v>179.42169200000001</v>
       </c>
-      <c r="T269" s="85">
+      <c r="T269" s="77">
         <v>180.54106100000001</v>
       </c>
-      <c r="U269" s="85">
+      <c r="U269" s="77">
         <v>180.158661</v>
       </c>
-      <c r="V269" s="85">
+      <c r="V269" s="77">
         <v>178.98571799999999</v>
       </c>
-      <c r="W269" s="85">
+      <c r="W269" s="77">
         <v>178.04853800000001</v>
       </c>
-      <c r="X269" s="85">
+      <c r="X269" s="77">
         <v>177.955994</v>
       </c>
-      <c r="Y269" s="85">
+      <c r="Y269" s="77">
         <v>178.03021200000001</v>
       </c>
-      <c r="Z269" s="85">
+      <c r="Z269" s="77">
         <v>176.14343299999999</v>
       </c>
-      <c r="AA269" s="85">
+      <c r="AA269" s="77">
         <v>173.144226</v>
       </c>
-      <c r="AB269" s="85">
+      <c r="AB269" s="77">
         <v>170.26071200000001</v>
       </c>
-      <c r="AC269" s="85">
+      <c r="AC269" s="77">
         <v>170.79948400000001</v>
       </c>
-      <c r="AD269" s="85">
+      <c r="AD269" s="77">
         <v>172.44551100000001</v>
       </c>
-      <c r="AE269" s="85">
+      <c r="AE269" s="77">
         <v>172.288971</v>
       </c>
-      <c r="AF269" s="85">
+      <c r="AF269" s="77">
         <v>170.28810100000001</v>
       </c>
-      <c r="AG269" s="86">
+      <c r="AG269" s="78">
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A270" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="271" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A271" t="s">
         <v>196</v>
       </c>
@@ -47674,7 +47726,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="272" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A272" t="s">
         <v>199</v>
       </c>
@@ -47772,7 +47824,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A273" t="s">
         <v>193</v>
       </c>
@@ -47870,7 +47922,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="274" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A274" t="s">
         <v>190</v>
       </c>
@@ -47968,7 +48020,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A275" t="s">
         <v>187</v>
       </c>
@@ -48066,7 +48118,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="276" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A276" t="s">
         <v>135</v>
       </c>
@@ -48164,7 +48216,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="277" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A277" t="s">
         <v>179</v>
       </c>
@@ -48262,7 +48314,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="278" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A278" t="s">
         <v>182</v>
       </c>
@@ -48360,7 +48412,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A279" t="s">
         <v>139</v>
       </c>
@@ -48458,7 +48510,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="280" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A280" t="s">
         <v>174</v>
       </c>
@@ -48556,7 +48608,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="281" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A281" t="s">
         <v>171</v>
       </c>
@@ -48654,7 +48706,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="282" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A282" t="s">
         <v>168</v>
       </c>
@@ -48752,105 +48804,105 @@
         <v>111</v>
       </c>
     </row>
-    <row r="283" spans="1:33" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="85" t="s">
+    <row r="283" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A283" s="77" t="s">
         <v>572</v>
       </c>
-      <c r="B283" s="85" t="s">
+      <c r="B283" s="77" t="s">
         <v>571</v>
       </c>
-      <c r="C283" s="85" t="s">
+      <c r="C283" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="D283" s="85" t="s">
+      <c r="D283" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F283" s="85">
+      <c r="F283" s="77">
         <v>313.60665899999998</v>
       </c>
-      <c r="G283" s="85">
+      <c r="G283" s="77">
         <v>319.41256700000002</v>
       </c>
-      <c r="H283" s="85">
+      <c r="H283" s="77">
         <v>342.18023699999998</v>
       </c>
-      <c r="I283" s="85">
+      <c r="I283" s="77">
         <v>358.62271099999998</v>
       </c>
-      <c r="J283" s="85">
+      <c r="J283" s="77">
         <v>349.476135</v>
       </c>
-      <c r="K283" s="85">
+      <c r="K283" s="77">
         <v>334.38430799999998</v>
       </c>
-      <c r="L283" s="85">
+      <c r="L283" s="77">
         <v>325.49188199999998</v>
       </c>
-      <c r="M283" s="85">
+      <c r="M283" s="77">
         <v>317.27001999999999</v>
       </c>
-      <c r="N283" s="85">
+      <c r="N283" s="77">
         <v>313.77713</v>
       </c>
-      <c r="O283" s="85">
+      <c r="O283" s="77">
         <v>314.72732500000001</v>
       </c>
-      <c r="P283" s="85">
+      <c r="P283" s="77">
         <v>313.967804</v>
       </c>
-      <c r="Q283" s="85">
+      <c r="Q283" s="77">
         <v>312.66604599999999</v>
       </c>
-      <c r="R283" s="85">
+      <c r="R283" s="77">
         <v>314.51275600000002</v>
       </c>
-      <c r="S283" s="85">
+      <c r="S283" s="77">
         <v>317.50311299999998</v>
       </c>
-      <c r="T283" s="85">
+      <c r="T283" s="77">
         <v>319.483948</v>
       </c>
-      <c r="U283" s="85">
+      <c r="U283" s="77">
         <v>318.80731200000002</v>
       </c>
-      <c r="V283" s="85">
+      <c r="V283" s="77">
         <v>316.731628</v>
       </c>
-      <c r="W283" s="85">
+      <c r="W283" s="77">
         <v>315.07318099999998</v>
       </c>
-      <c r="X283" s="85">
+      <c r="X283" s="77">
         <v>314.909424</v>
       </c>
-      <c r="Y283" s="85">
+      <c r="Y283" s="77">
         <v>315.04077100000001</v>
       </c>
-      <c r="Z283" s="85">
+      <c r="Z283" s="77">
         <v>311.70193499999999</v>
       </c>
-      <c r="AA283" s="85">
+      <c r="AA283" s="77">
         <v>306.39459199999999</v>
       </c>
-      <c r="AB283" s="85">
+      <c r="AB283" s="77">
         <v>301.29199199999999</v>
       </c>
-      <c r="AC283" s="85">
+      <c r="AC283" s="77">
         <v>302.245361</v>
       </c>
-      <c r="AD283" s="85">
+      <c r="AD283" s="77">
         <v>305.15811200000002</v>
       </c>
-      <c r="AE283" s="85">
+      <c r="AE283" s="77">
         <v>304.88110399999999</v>
       </c>
-      <c r="AF283" s="85">
+      <c r="AF283" s="77">
         <v>301.34033199999999</v>
       </c>
-      <c r="AG283" s="86">
+      <c r="AG283" s="78">
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A284" t="s">
         <v>130</v>
       </c>
@@ -48948,12 +49000,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A285" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="286" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A286" t="s">
         <v>567</v>
       </c>
@@ -49051,7 +49103,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="287" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A287" t="s">
         <v>550</v>
       </c>
@@ -49149,12 +49201,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="288" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A288" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="289" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A289" t="s">
         <v>527</v>
       </c>
@@ -49252,7 +49304,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="290" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A290" t="s">
         <v>524</v>
       </c>
@@ -49350,7 +49402,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="291" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A291" t="s">
         <v>521</v>
       </c>
@@ -49448,7 +49500,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="292" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A292" t="s">
         <v>518</v>
       </c>
@@ -49546,12 +49598,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="293" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A293" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="294" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A294" t="s">
         <v>554</v>
       </c>
@@ -49649,7 +49701,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A295" t="s">
         <v>550</v>
       </c>
@@ -49747,12 +49799,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="296" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A296" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="297" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A297" t="s">
         <v>527</v>
       </c>
@@ -49850,7 +49902,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A298" t="s">
         <v>524</v>
       </c>
@@ -49948,7 +50000,7 @@
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A299" t="s">
         <v>521</v>
       </c>
@@ -50046,7 +50098,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="300" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A300" t="s">
         <v>518</v>
       </c>
@@ -50144,12 +50196,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="301" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A301" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="302" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A302" t="s">
         <v>538</v>
       </c>
@@ -50247,7 +50299,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A303" t="s">
         <v>535</v>
       </c>
@@ -50345,7 +50397,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A304" t="s">
         <v>532</v>
       </c>
@@ -50443,12 +50495,12 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A305" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A306" t="s">
         <v>527</v>
       </c>
@@ -50546,7 +50598,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A307" t="s">
         <v>524</v>
       </c>
@@ -50644,7 +50696,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A308" t="s">
         <v>521</v>
       </c>
@@ -50742,7 +50794,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A309" t="s">
         <v>518</v>
       </c>
@@ -50851,7 +50903,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50860,20 +50912,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P48"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="30.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="3" customWidth="1"/>
-    <col min="6" max="14" width="9.140625" style="3"/>
-    <col min="15" max="15" width="15.42578125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="22.5703125" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="30.1328125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.7265625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="3" customWidth="1"/>
+    <col min="6" max="14" width="9.1328125" style="3"/>
+    <col min="15" max="15" width="15.40625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="22.54296875" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.1328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A1" s="6" t="s">
         <v>48</v>
       </c>
@@ -50882,7 +50934,7 @@
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="59" x14ac:dyDescent="0.75">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -50901,7 +50953,7 @@
       <c r="O2" s="72"/>
       <c r="P2" s="73"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A3" s="3">
         <v>13</v>
       </c>
@@ -50922,16 +50974,16 @@
       </c>
       <c r="P3" s="73"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.75">
       <c r="P4" s="73"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A5" s="10" t="s">
         <v>51</v>
       </c>
       <c r="P5" s="73"/>
     </row>
-    <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A6" s="7" t="s">
         <v>55</v>
       </c>
@@ -50946,7 +50998,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A7" s="68">
         <v>28</v>
       </c>
@@ -50961,7 +51013,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.75">
       <c r="A10" s="10" t="s">
         <v>52</v>
       </c>
@@ -50970,14 +51022,14 @@
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A12" s="9" t="s">
         <v>30</v>
       </c>
@@ -50985,7 +51037,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A13" s="9" t="s">
         <v>32</v>
       </c>
@@ -50993,7 +51045,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="9" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
@@ -51001,17 +51053,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A15" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="9" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A16" s="18">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
@@ -51020,7 +51072,7 @@
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="15" t="s">
         <v>6</v>
       </c>
@@ -51031,7 +51083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -51042,7 +51094,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -51053,7 +51105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A22"/>
       <c r="B22" s="11" t="s">
         <v>22</v>
@@ -51062,17 +51114,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="10" t="s">
         <v>9</v>
       </c>
@@ -51081,7 +51133,7 @@
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A27" s="15" t="s">
         <v>6</v>
       </c>
@@ -51092,7 +51144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -51103,7 +51155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A30" s="10" t="s">
         <v>54</v>
       </c>
@@ -51112,7 +51164,7 @@
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A31" s="21" t="s">
         <v>39</v>
       </c>
@@ -51129,7 +51181,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="20">
         <v>1997</v>
       </c>
@@ -51142,7 +51194,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="20">
         <v>1998</v>
       </c>
@@ -51161,7 +51213,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="20">
         <v>1999</v>
       </c>
@@ -51180,7 +51232,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="20">
         <v>2000</v>
       </c>
@@ -51199,7 +51251,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="20">
         <v>2001</v>
       </c>
@@ -51218,7 +51270,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="20">
         <v>2002</v>
       </c>
@@ -51237,7 +51289,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="20">
         <v>2003</v>
       </c>
@@ -51256,7 +51308,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="20">
         <v>2004</v>
       </c>
@@ -51275,7 +51327,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="20">
         <v>2005</v>
       </c>
@@ -51294,7 +51346,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="20">
         <v>2006</v>
       </c>
@@ -51313,7 +51365,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A42" s="25">
         <v>2007</v>
       </c>
@@ -51332,14 +51384,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -51347,7 +51399,7 @@
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="28">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -51356,13 +51408,13 @@
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A47" s="36" t="s">
         <v>44</v>
       </c>
@@ -51370,7 +51422,7 @@
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A48" s="35">
         <f>1/A45</f>
         <v>17.22332068760786</v>

--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA827B10-E881-4A82-AA32-F77783B36D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3614F806-3FDA-4A1A-80BD-28E5ADF743DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{661390DE-D06E-402F-B49F-05F85B2DF025}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="10" xr2:uid="{661390DE-D06E-402F-B49F-05F85B2DF025}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -4500,7 +4500,17 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4515,16 +4525,6 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="63">
     <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
@@ -4927,17 +4927,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="132.26953125" customWidth="1"/>
+    <col min="2" max="2" width="132.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4945,237 +4945,237 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="75" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="9">
         <v>2016</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="9">
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="9">
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="9">
         <v>2013</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="9">
         <v>2009</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.75">
-      <c r="B47" s="88" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="80" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.75">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="9">
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>93</v>
       </c>
@@ -5194,12 +5194,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC31426-123E-4577-A9C8-93E89562BFE4}">
   <dimension ref="A2:C21"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>472289.185</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>14603680.663999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -5226,13 +5226,13 @@
         <v>30.921056691145701</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="37"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="37"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>395582.73299999995</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>155</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>9076094</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -5263,10 +5263,10 @@
         <v>22.943605073884765</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="37"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>156</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>313606.65899999999</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>5553924</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>17.709840784981548</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>158</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>73000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>12.166666666666668</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -5354,14 +5354,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
         <v>94</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -5380,11 +5380,10 @@
         <v>17</v>
       </c>
       <c r="C2" s="70">
-        <f>B2</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -5397,7 +5396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -5410,7 +5409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -5423,7 +5422,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -5436,7 +5435,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -5460,7 +5459,7 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5469,72 +5468,72 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB61"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.40625" customWidth="1"/>
-    <col min="2" max="27" width="7.7265625" customWidth="1"/>
-    <col min="28" max="28" width="7.1328125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="27" width="7.7109375" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="82"/>
-      <c r="AJ1" s="82"/>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AN1" s="82"/>
-      <c r="AO1" s="82"/>
-      <c r="AP1" s="82"/>
-      <c r="AQ1" s="82"/>
-      <c r="AR1" s="82"/>
-      <c r="AS1" s="82"/>
-      <c r="AT1" s="82"/>
-      <c r="AU1" s="82"/>
-      <c r="AV1" s="82"/>
-      <c r="AW1" s="82"/>
-      <c r="AX1" s="82"/>
-      <c r="AY1" s="82"/>
-      <c r="AZ1" s="82"/>
-      <c r="BA1" s="82"/>
-      <c r="BB1" s="82"/>
-    </row>
-    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
+      <c r="AC1" s="86"/>
+      <c r="AD1" s="86"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="86"/>
+      <c r="AK1" s="86"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="86"/>
+      <c r="AN1" s="86"/>
+      <c r="AO1" s="86"/>
+      <c r="AP1" s="86"/>
+      <c r="AQ1" s="86"/>
+      <c r="AR1" s="86"/>
+      <c r="AS1" s="86"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
+      <c r="BB1" s="86"/>
+    </row>
+    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
       <c r="B2" s="39">
         <v>1980</v>
@@ -5644,7 +5643,7 @@
       <c r="BA2" s="45"/>
       <c r="BB2" s="46"/>
     </row>
-    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47" t="s">
         <v>61</v>
       </c>
@@ -5756,7 +5755,7 @@
       <c r="BA3" s="48"/>
       <c r="BB3" s="48"/>
     </row>
-    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
         <v>63</v>
       </c>
@@ -5868,7 +5867,7 @@
       <c r="BA4" s="52"/>
       <c r="BB4" s="52"/>
     </row>
-    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>64</v>
       </c>
@@ -5980,7 +5979,7 @@
       <c r="BA5" s="52"/>
       <c r="BB5" s="52"/>
     </row>
-    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>65</v>
       </c>
@@ -6092,7 +6091,7 @@
       <c r="BA6" s="52"/>
       <c r="BB6" s="52"/>
     </row>
-    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>66</v>
       </c>
@@ -6204,7 +6203,7 @@
       <c r="BA7" s="52"/>
       <c r="BB7" s="52"/>
     </row>
-    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
         <v>67</v>
       </c>
@@ -6316,7 +6315,7 @@
       <c r="BA8" s="52"/>
       <c r="BB8" s="52"/>
     </row>
-    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="53" t="s">
         <v>68</v>
       </c>
@@ -6374,7 +6373,7 @@
       <c r="BA9" s="54"/>
       <c r="BB9" s="54"/>
     </row>
-    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50" t="s">
         <v>63</v>
       </c>
@@ -6488,7 +6487,7 @@
       <c r="BA10" s="56"/>
       <c r="BB10" s="56"/>
     </row>
-    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>64</v>
       </c>
@@ -6600,7 +6599,7 @@
       <c r="BA11" s="56"/>
       <c r="BB11" s="56"/>
     </row>
-    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>65</v>
       </c>
@@ -6712,7 +6711,7 @@
       <c r="BA12" s="56"/>
       <c r="BB12" s="56"/>
     </row>
-    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50" t="s">
         <v>66</v>
       </c>
@@ -6824,7 +6823,7 @@
       <c r="BA13" s="56"/>
       <c r="BB13" s="56"/>
     </row>
-    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50" t="s">
         <v>67</v>
       </c>
@@ -6936,7 +6935,7 @@
       <c r="BA14" s="56"/>
       <c r="BB14" s="56"/>
     </row>
-    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>69</v>
       </c>
@@ -6994,7 +6993,7 @@
       <c r="BA15" s="58"/>
       <c r="BB15" s="58"/>
     </row>
-    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
         <v>63</v>
       </c>
@@ -7106,7 +7105,7 @@
       <c r="BA16" s="59"/>
       <c r="BB16" s="59"/>
     </row>
-    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>64</v>
       </c>
@@ -7218,7 +7217,7 @@
       <c r="BA17" s="59"/>
       <c r="BB17" s="59"/>
     </row>
-    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
         <v>65</v>
       </c>
@@ -7330,7 +7329,7 @@
       <c r="BA18" s="59"/>
       <c r="BB18" s="59"/>
     </row>
-    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50" t="s">
         <v>66</v>
       </c>
@@ -7442,7 +7441,7 @@
       <c r="BA19" s="59"/>
       <c r="BB19" s="59"/>
     </row>
-    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="60" t="s">
         <v>67</v>
       </c>
@@ -7554,233 +7553,233 @@
       <c r="BA20" s="59"/>
       <c r="BB20" s="59"/>
     </row>
-    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A21" s="83" t="s">
+    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-    </row>
-    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="84"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-    </row>
-    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A23" s="84" t="s">
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="87"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="87"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+    </row>
+    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="88"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+    </row>
+    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-    </row>
-    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A24" s="80" t="s">
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+    </row>
+    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="80"/>
-    </row>
-    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A25" s="80" t="s">
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
+    </row>
+    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
-    </row>
-    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A26" s="85" t="s">
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
+    </row>
+    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-    </row>
-    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A27" s="85"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="85"/>
-    </row>
-    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A28" s="86" t="s">
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+    </row>
+    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="82"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+    </row>
+    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="86"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-    </row>
-    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A29" s="87" t="s">
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+    </row>
+    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="87"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="87"/>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-    </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.75"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.75"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="84"/>
+    </row>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AC1:BB1"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="A22:Q22"/>
     <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7789,32 +7788,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B98BD0-2AB5-48C3-A94B-802255ACBC65}">
   <dimension ref="A1:AG66"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -7912,12 +7911,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>101</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -8023,7 +8022,7 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -8121,7 +8120,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -8219,12 +8218,12 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -8322,7 +8321,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -8420,7 +8419,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -8518,7 +8517,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -8616,7 +8615,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -8714,7 +8713,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -8812,7 +8811,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -8910,7 +8909,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -9106,7 +9105,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -9204,7 +9203,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -9302,7 +9301,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -9400,7 +9399,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -9498,7 +9497,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -9596,7 +9595,7 @@
         <v>-3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -9694,7 +9693,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>364</v>
       </c>
@@ -9792,7 +9791,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -9890,17 +9889,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -9998,7 +9997,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -10096,7 +10095,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>124</v>
       </c>
@@ -10194,12 +10193,12 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -10297,7 +10296,7 @@
         <v>-4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -10395,7 +10394,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>232</v>
       </c>
@@ -10493,7 +10492,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>229</v>
       </c>
@@ -10591,7 +10590,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -10689,7 +10688,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -10787,7 +10786,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -10885,7 +10884,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -10983,7 +10982,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -11081,7 +11080,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -11179,7 +11178,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>116</v>
       </c>
@@ -11375,7 +11374,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>117</v>
       </c>
@@ -11473,7 +11472,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -11571,7 +11570,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -11669,7 +11668,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -11767,7 +11766,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>127</v>
       </c>
@@ -11865,7 +11864,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>148</v>
       </c>
@@ -11963,12 +11962,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -12066,7 +12065,7 @@
         <v>-5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>196</v>
       </c>
@@ -12164,7 +12163,7 @@
         <v>-5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>193</v>
       </c>
@@ -12262,7 +12261,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>190</v>
       </c>
@@ -12360,7 +12359,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -12458,7 +12457,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>135</v>
       </c>
@@ -12556,7 +12555,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>182</v>
       </c>
@@ -12654,7 +12653,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -12752,7 +12751,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>139</v>
       </c>
@@ -12850,7 +12849,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>174</v>
       </c>
@@ -12948,7 +12947,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>171</v>
       </c>
@@ -13046,7 +13045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>168</v>
       </c>
@@ -13144,7 +13143,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>291</v>
       </c>
@@ -13250,32 +13249,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6F1E4F-C2E1-4AC1-9426-39A4D1D07272}">
   <dimension ref="A1:AG63"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -13373,17 +13372,17 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -13481,7 +13480,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -13579,7 +13578,7 @@
         <v>-0.123</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -13677,12 +13676,12 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -13780,7 +13779,7 @@
         <v>-0.112</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -13878,7 +13877,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -13976,7 +13975,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -14074,7 +14073,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -14172,7 +14171,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -14270,7 +14269,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -14368,7 +14367,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -14466,7 +14465,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -14564,7 +14563,7 @@
         <v>-8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -14662,7 +14661,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -14760,7 +14759,7 @@
         <v>-6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -14858,7 +14857,7 @@
         <v>-6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -14956,7 +14955,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -15054,7 +15053,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -15152,7 +15151,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>247</v>
       </c>
@@ -15250,17 +15249,17 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -15358,7 +15357,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -15456,7 +15455,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -15554,12 +15553,12 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -15657,7 +15656,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>235</v>
       </c>
@@ -15755,7 +15754,7 @@
         <v>-9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>232</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>229</v>
       </c>
@@ -15951,7 +15950,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -16049,7 +16048,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -16147,7 +16146,7 @@
         <v>0.17599999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -16245,7 +16244,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -16343,7 +16342,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -16441,7 +16440,7 @@
         <v>-6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -16539,7 +16538,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -16637,7 +16636,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -16735,7 +16734,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -16833,7 +16832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -16931,7 +16930,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>126</v>
       </c>
@@ -17029,7 +17028,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>204</v>
       </c>
@@ -17127,7 +17126,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>148</v>
       </c>
@@ -17225,7 +17224,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>199</v>
       </c>
@@ -17323,7 +17322,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>196</v>
       </c>
@@ -17421,7 +17420,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>193</v>
       </c>
@@ -17519,7 +17518,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>190</v>
       </c>
@@ -17617,7 +17616,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>187</v>
       </c>
@@ -17715,7 +17714,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>135</v>
       </c>
@@ -17813,7 +17812,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -17911,7 +17910,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>179</v>
       </c>
@@ -18009,7 +18008,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>139</v>
       </c>
@@ -18107,7 +18106,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>174</v>
       </c>
@@ -18205,7 +18204,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>171</v>
       </c>
@@ -18303,7 +18302,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>168</v>
       </c>
@@ -18401,7 +18400,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>165</v>
       </c>
@@ -18507,29 +18506,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D130767C-6285-4C0E-BDF9-7A9F61BDC9F4}">
   <dimension ref="A1:AG67"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -18627,17 +18626,17 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -18735,7 +18734,7 @@
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -18833,7 +18832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -18931,12 +18930,12 @@
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -19034,7 +19033,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -19132,7 +19131,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -19230,7 +19229,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -19328,7 +19327,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -19426,7 +19425,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -19524,7 +19523,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -19622,7 +19621,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -19720,7 +19719,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -19818,7 +19817,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -19916,7 +19915,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -20014,7 +20013,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -20112,7 +20111,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -20210,7 +20209,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -20308,7 +20307,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -20406,7 +20405,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>364</v>
       </c>
@@ -20504,7 +20503,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -20602,17 +20601,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -20710,7 +20709,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -20808,7 +20807,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>124</v>
       </c>
@@ -20906,12 +20905,12 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -21009,7 +21008,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -21107,7 +21106,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>232</v>
       </c>
@@ -21205,7 +21204,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>229</v>
       </c>
@@ -21303,7 +21302,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -21401,7 +21400,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -21499,7 +21498,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -21597,7 +21596,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -21695,7 +21694,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -21793,7 +21792,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -21891,7 +21890,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -21989,7 +21988,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>116</v>
       </c>
@@ -22087,7 +22086,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>117</v>
       </c>
@@ -22185,7 +22184,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -22283,7 +22282,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -22381,7 +22380,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -22479,7 +22478,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>127</v>
       </c>
@@ -22577,7 +22576,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>433</v>
       </c>
@@ -22675,7 +22674,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -22773,7 +22772,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>129</v>
       </c>
@@ -22871,7 +22870,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>130</v>
       </c>
@@ -22879,7 +22878,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>132</v>
       </c>
@@ -22977,7 +22976,7 @@
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>133</v>
       </c>
@@ -23075,7 +23074,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>134</v>
       </c>
@@ -23173,7 +23172,7 @@
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>135</v>
       </c>
@@ -23271,7 +23270,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -23369,7 +23368,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>137</v>
       </c>
@@ -23467,7 +23466,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>138</v>
       </c>
@@ -23565,7 +23564,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -23663,7 +23662,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>140</v>
       </c>
@@ -23761,7 +23760,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>141</v>
       </c>
@@ -23859,7 +23858,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -23957,7 +23956,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -24063,33 +24062,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00A17A9-9291-44B9-93C2-28F7BD4C132B}">
   <dimension ref="A1:AG309"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -24187,22 +24186,22 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>196</v>
       </c>
@@ -24300,7 +24299,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>199</v>
       </c>
@@ -24398,7 +24397,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>193</v>
       </c>
@@ -24496,7 +24495,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>190</v>
       </c>
@@ -24594,7 +24593,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>187</v>
       </c>
@@ -24692,7 +24691,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>135</v>
       </c>
@@ -24790,7 +24789,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -24888,7 +24887,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -24986,7 +24985,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>139</v>
       </c>
@@ -25084,7 +25083,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>174</v>
       </c>
@@ -25182,7 +25181,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -25280,7 +25279,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -25378,7 +25377,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>628</v>
       </c>
@@ -25476,12 +25475,12 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>196</v>
       </c>
@@ -25579,7 +25578,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -25677,7 +25676,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>193</v>
       </c>
@@ -25775,7 +25774,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>190</v>
       </c>
@@ -25873,7 +25872,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>187</v>
       </c>
@@ -25971,7 +25970,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -26069,7 +26068,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>179</v>
       </c>
@@ -26167,7 +26166,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -26265,7 +26264,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -26363,7 +26362,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -26461,7 +26460,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>171</v>
       </c>
@@ -26559,7 +26558,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>168</v>
       </c>
@@ -26657,7 +26656,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="77" t="s">
         <v>600</v>
       </c>
@@ -26755,12 +26754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>196</v>
       </c>
@@ -26858,7 +26857,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>199</v>
       </c>
@@ -26956,7 +26955,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>193</v>
       </c>
@@ -27054,7 +27053,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -27152,7 +27151,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>187</v>
       </c>
@@ -27250,7 +27249,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -27348,7 +27347,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>179</v>
       </c>
@@ -27446,7 +27445,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>182</v>
       </c>
@@ -27544,7 +27543,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>139</v>
       </c>
@@ -27642,7 +27641,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>174</v>
       </c>
@@ -27740,7 +27739,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>171</v>
       </c>
@@ -27838,7 +27837,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>168</v>
       </c>
@@ -27936,7 +27935,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>572</v>
       </c>
@@ -28034,7 +28033,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1017</v>
       </c>
@@ -28132,17 +28131,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>196</v>
       </c>
@@ -28240,7 +28239,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -28338,7 +28337,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>193</v>
       </c>
@@ -28436,7 +28435,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>190</v>
       </c>
@@ -28534,7 +28533,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>187</v>
       </c>
@@ -28632,7 +28631,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>135</v>
       </c>
@@ -28730,7 +28729,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>179</v>
       </c>
@@ -28828,7 +28827,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>182</v>
       </c>
@@ -28926,7 +28925,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>139</v>
       </c>
@@ -29024,7 +29023,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -29122,7 +29121,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>171</v>
       </c>
@@ -29220,7 +29219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>168</v>
       </c>
@@ -29318,7 +29317,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>628</v>
       </c>
@@ -29416,12 +29415,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>196</v>
       </c>
@@ -29519,7 +29518,7 @@
         <v>-2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -29617,7 +29616,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -29715,7 +29714,7 @@
         <v>-0.104</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -29813,7 +29812,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>187</v>
       </c>
@@ -29911,7 +29910,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>135</v>
       </c>
@@ -30009,7 +30008,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>179</v>
       </c>
@@ -30107,7 +30106,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>182</v>
       </c>
@@ -30205,7 +30204,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>139</v>
       </c>
@@ -30303,7 +30302,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>174</v>
       </c>
@@ -30401,7 +30400,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -30499,7 +30498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>168</v>
       </c>
@@ -30597,7 +30596,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>600</v>
       </c>
@@ -30695,12 +30694,12 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>196</v>
       </c>
@@ -30798,7 +30797,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>199</v>
       </c>
@@ -30896,7 +30895,7 @@
         <v>-5.5E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>193</v>
       </c>
@@ -30994,7 +30993,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>190</v>
       </c>
@@ -31092,7 +31091,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>187</v>
       </c>
@@ -31190,7 +31189,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>135</v>
       </c>
@@ -31288,7 +31287,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>179</v>
       </c>
@@ -31386,7 +31385,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>182</v>
       </c>
@@ -31484,7 +31483,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>139</v>
       </c>
@@ -31582,7 +31581,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>174</v>
       </c>
@@ -31680,7 +31679,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>171</v>
       </c>
@@ -31778,7 +31777,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>168</v>
       </c>
@@ -31876,7 +31875,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>572</v>
       </c>
@@ -31974,7 +31973,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>653</v>
       </c>
@@ -31985,7 +31984,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>196</v>
       </c>
@@ -32083,7 +32082,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>199</v>
       </c>
@@ -32181,7 +32180,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -32279,7 +32278,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>190</v>
       </c>
@@ -32377,7 +32376,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>187</v>
       </c>
@@ -32475,7 +32474,7 @@
         <v>-0.109</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -32573,7 +32572,7 @@
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>179</v>
       </c>
@@ -32671,7 +32670,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>182</v>
       </c>
@@ -32769,7 +32768,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>139</v>
       </c>
@@ -32867,7 +32866,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>174</v>
       </c>
@@ -32965,7 +32964,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>171</v>
       </c>
@@ -33063,7 +33062,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>168</v>
       </c>
@@ -33161,7 +33160,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>908</v>
       </c>
@@ -33259,17 +33258,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>196</v>
       </c>
@@ -33367,7 +33366,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>199</v>
       </c>
@@ -33465,7 +33464,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>193</v>
       </c>
@@ -33563,7 +33562,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>190</v>
       </c>
@@ -33661,7 +33660,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>187</v>
       </c>
@@ -33759,7 +33758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>135</v>
       </c>
@@ -33857,7 +33856,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>179</v>
       </c>
@@ -33955,7 +33954,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>182</v>
       </c>
@@ -34053,7 +34052,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>139</v>
       </c>
@@ -34151,7 +34150,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>174</v>
       </c>
@@ -34249,7 +34248,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>171</v>
       </c>
@@ -34347,7 +34346,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>168</v>
       </c>
@@ -34445,7 +34444,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>717</v>
       </c>
@@ -34540,12 +34539,12 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>196</v>
       </c>
@@ -34643,7 +34642,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>199</v>
       </c>
@@ -34741,7 +34740,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>193</v>
       </c>
@@ -34839,7 +34838,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>190</v>
       </c>
@@ -34937,7 +34936,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>187</v>
       </c>
@@ -35035,7 +35034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>135</v>
       </c>
@@ -35133,7 +35132,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>179</v>
       </c>
@@ -35231,7 +35230,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>182</v>
       </c>
@@ -35329,7 +35328,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -35427,7 +35426,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>174</v>
       </c>
@@ -35525,7 +35524,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>171</v>
       </c>
@@ -35623,7 +35622,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -35721,7 +35720,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>689</v>
       </c>
@@ -35816,12 +35815,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>196</v>
       </c>
@@ -35919,7 +35918,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>199</v>
       </c>
@@ -36017,7 +36016,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>193</v>
       </c>
@@ -36115,7 +36114,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>190</v>
       </c>
@@ -36213,7 +36212,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>187</v>
       </c>
@@ -36311,7 +36310,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>135</v>
       </c>
@@ -36409,7 +36408,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -36507,7 +36506,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>182</v>
       </c>
@@ -36605,7 +36604,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>139</v>
       </c>
@@ -36703,7 +36702,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -36801,7 +36800,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>171</v>
       </c>
@@ -36899,7 +36898,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -36997,7 +36996,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>660</v>
       </c>
@@ -37092,7 +37091,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>657</v>
       </c>
@@ -37187,17 +37186,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>196</v>
       </c>
@@ -37295,7 +37294,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -37393,7 +37392,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>193</v>
       </c>
@@ -37491,7 +37490,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -37589,7 +37588,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>187</v>
       </c>
@@ -37687,7 +37686,7 @@
         <v>-6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>135</v>
       </c>
@@ -37785,7 +37784,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>179</v>
       </c>
@@ -37883,7 +37882,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>182</v>
       </c>
@@ -37981,7 +37980,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -38079,7 +38078,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>174</v>
       </c>
@@ -38177,7 +38176,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -38275,7 +38274,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -38373,7 +38372,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="166" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>628</v>
       </c>
@@ -38471,12 +38470,12 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>196</v>
       </c>
@@ -38574,7 +38573,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -38672,7 +38671,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>193</v>
       </c>
@@ -38770,7 +38769,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -38868,7 +38867,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>187</v>
       </c>
@@ -38966,7 +38965,7 @@
         <v>-5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>135</v>
       </c>
@@ -39064,7 +39063,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>179</v>
       </c>
@@ -39162,7 +39161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -39260,7 +39259,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>139</v>
       </c>
@@ -39358,7 +39357,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>174</v>
       </c>
@@ -39456,7 +39455,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>171</v>
       </c>
@@ -39554,7 +39553,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>168</v>
       </c>
@@ -39652,7 +39651,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="180" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>600</v>
       </c>
@@ -39750,12 +39749,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -39853,7 +39852,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -39951,7 +39950,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>193</v>
       </c>
@@ -40049,7 +40048,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -40147,7 +40146,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>187</v>
       </c>
@@ -40245,7 +40244,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>135</v>
       </c>
@@ -40343,7 +40342,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>179</v>
       </c>
@@ -40441,7 +40440,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>182</v>
       </c>
@@ -40539,7 +40538,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>139</v>
       </c>
@@ -40637,7 +40636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>174</v>
       </c>
@@ -40735,7 +40734,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>171</v>
       </c>
@@ -40833,7 +40832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>168</v>
       </c>
@@ -40931,7 +40930,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="194" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="77" t="s">
         <v>572</v>
       </c>
@@ -41029,7 +41028,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>746</v>
       </c>
@@ -41127,22 +41126,22 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>196</v>
       </c>
@@ -41240,7 +41239,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -41338,7 +41337,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>193</v>
       </c>
@@ -41436,7 +41435,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>190</v>
       </c>
@@ -41534,7 +41533,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>187</v>
       </c>
@@ -41632,7 +41631,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>135</v>
       </c>
@@ -41730,7 +41729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>179</v>
       </c>
@@ -41828,7 +41827,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>182</v>
       </c>
@@ -41926,7 +41925,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>139</v>
       </c>
@@ -42024,7 +42023,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>174</v>
       </c>
@@ -42122,7 +42121,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>171</v>
       </c>
@@ -42220,7 +42219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>168</v>
       </c>
@@ -42318,7 +42317,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>717</v>
       </c>
@@ -42413,12 +42412,12 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>196</v>
       </c>
@@ -42516,7 +42515,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -42614,7 +42613,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>193</v>
       </c>
@@ -42712,7 +42711,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -42810,7 +42809,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>187</v>
       </c>
@@ -42908,7 +42907,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>135</v>
       </c>
@@ -43006,7 +43005,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>179</v>
       </c>
@@ -43104,7 +43103,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>182</v>
       </c>
@@ -43202,7 +43201,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>139</v>
       </c>
@@ -43300,7 +43299,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>174</v>
       </c>
@@ -43398,7 +43397,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>171</v>
       </c>
@@ -43496,7 +43495,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>168</v>
       </c>
@@ -43594,7 +43593,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>689</v>
       </c>
@@ -43689,12 +43688,12 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -43792,7 +43791,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>199</v>
       </c>
@@ -43890,7 +43889,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>193</v>
       </c>
@@ -43988,7 +43987,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -44086,7 +44085,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>187</v>
       </c>
@@ -44184,7 +44183,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="232" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>135</v>
       </c>
@@ -44282,7 +44281,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>179</v>
       </c>
@@ -44380,7 +44379,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>182</v>
       </c>
@@ -44478,7 +44477,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>139</v>
       </c>
@@ -44576,7 +44575,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>174</v>
       </c>
@@ -44674,7 +44673,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>171</v>
       </c>
@@ -44772,7 +44771,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>168</v>
       </c>
@@ -44870,7 +44869,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>660</v>
       </c>
@@ -44965,7 +44964,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>657</v>
       </c>
@@ -45060,17 +45059,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>196</v>
       </c>
@@ -45168,7 +45167,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>199</v>
       </c>
@@ -45266,7 +45265,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>193</v>
       </c>
@@ -45364,7 +45363,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>190</v>
       </c>
@@ -45462,7 +45461,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>187</v>
       </c>
@@ -45560,7 +45559,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>135</v>
       </c>
@@ -45658,7 +45657,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>179</v>
       </c>
@@ -45756,7 +45755,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>182</v>
       </c>
@@ -45854,7 +45853,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>139</v>
       </c>
@@ -45952,7 +45951,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>174</v>
       </c>
@@ -46050,7 +46049,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>171</v>
       </c>
@@ -46148,7 +46147,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>168</v>
       </c>
@@ -46246,7 +46245,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="255" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="77" t="s">
         <v>628</v>
       </c>
@@ -46344,12 +46343,12 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="257" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>196</v>
       </c>
@@ -46447,7 +46446,7 @@
         <v>-2.3E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>199</v>
       </c>
@@ -46545,7 +46544,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>193</v>
       </c>
@@ -46643,7 +46642,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>190</v>
       </c>
@@ -46741,7 +46740,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>187</v>
       </c>
@@ -46839,7 +46838,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>135</v>
       </c>
@@ -46937,7 +46936,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>179</v>
       </c>
@@ -47035,7 +47034,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>182</v>
       </c>
@@ -47133,7 +47132,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="265" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>139</v>
       </c>
@@ -47231,7 +47230,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="266" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>174</v>
       </c>
@@ -47329,7 +47328,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="267" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>171</v>
       </c>
@@ -47427,7 +47426,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="268" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>168</v>
       </c>
@@ -47525,7 +47524,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="269" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="77" t="s">
         <v>600</v>
       </c>
@@ -47623,12 +47622,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="271" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>196</v>
       </c>
@@ -47726,7 +47725,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="272" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>199</v>
       </c>
@@ -47824,7 +47823,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="273" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>193</v>
       </c>
@@ -47922,7 +47921,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="274" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="274" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>190</v>
       </c>
@@ -48020,7 +48019,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>187</v>
       </c>
@@ -48118,7 +48117,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="276" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>135</v>
       </c>
@@ -48216,7 +48215,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="277" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>179</v>
       </c>
@@ -48314,7 +48313,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="278" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="278" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>182</v>
       </c>
@@ -48412,7 +48411,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="279" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>139</v>
       </c>
@@ -48510,7 +48509,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="280" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="280" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>174</v>
       </c>
@@ -48608,7 +48607,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="281" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="281" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>171</v>
       </c>
@@ -48706,7 +48705,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="282" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="282" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>168</v>
       </c>
@@ -48804,7 +48803,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="283" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="283" spans="1:33" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="77" t="s">
         <v>572</v>
       </c>
@@ -48902,7 +48901,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="284" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>130</v>
       </c>
@@ -49000,12 +48999,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="285" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="286" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="286" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>567</v>
       </c>
@@ -49103,7 +49102,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="287" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="287" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>550</v>
       </c>
@@ -49201,12 +49200,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="288" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="288" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="289" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="289" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>527</v>
       </c>
@@ -49304,7 +49303,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="290" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="290" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>524</v>
       </c>
@@ -49402,7 +49401,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="291" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="291" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>521</v>
       </c>
@@ -49500,7 +49499,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="292" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="292" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>518</v>
       </c>
@@ -49598,12 +49597,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="293" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="293" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="294" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="294" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>554</v>
       </c>
@@ -49701,7 +49700,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="295" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>550</v>
       </c>
@@ -49799,12 +49798,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="296" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="296" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="297" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="297" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>527</v>
       </c>
@@ -49902,7 +49901,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="298" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>524</v>
       </c>
@@ -50000,7 +49999,7 @@
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="299" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>521</v>
       </c>
@@ -50098,7 +50097,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="300" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="300" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>518</v>
       </c>
@@ -50196,12 +50195,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="301" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="301" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="302" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="302" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>538</v>
       </c>
@@ -50299,7 +50298,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="303" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>535</v>
       </c>
@@ -50397,7 +50396,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="304" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>532</v>
       </c>
@@ -50495,12 +50494,12 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>527</v>
       </c>
@@ -50598,7 +50597,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>524</v>
       </c>
@@ -50696,7 +50695,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="308" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>521</v>
       </c>
@@ -50794,7 +50793,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.75">
+    <row r="309" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>518</v>
       </c>
@@ -50903,7 +50902,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50912,20 +50911,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P48"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.26953125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.7265625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="3" customWidth="1"/>
-    <col min="6" max="14" width="9.1328125" style="3"/>
-    <col min="15" max="15" width="15.40625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="22.54296875" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.1328125" style="3"/>
+    <col min="1" max="1" width="30.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="3" customWidth="1"/>
+    <col min="6" max="14" width="9.140625" style="3"/>
+    <col min="15" max="15" width="15.42578125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>48</v>
       </c>
@@ -50934,7 +50933,7 @@
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="59" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -50953,7 +50952,7 @@
       <c r="O2" s="72"/>
       <c r="P2" s="73"/>
     </row>
-    <row r="3" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>13</v>
       </c>
@@ -50974,16 +50973,16 @@
       </c>
       <c r="P3" s="73"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="P4" s="73"/>
     </row>
-    <row r="5" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>51</v>
       </c>
       <c r="P5" s="73"/>
     </row>
-    <row r="6" spans="1:16" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>55</v>
       </c>
@@ -50998,7 +50997,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
         <v>28</v>
       </c>
@@ -51013,7 +51012,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>52</v>
       </c>
@@ -51022,14 +51021,14 @@
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>30</v>
       </c>
@@ -51037,7 +51036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>32</v>
       </c>
@@ -51045,7 +51044,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="9" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="14" spans="1:16" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
@@ -51053,17 +51052,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="9" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="16" spans="1:16" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
@@ -51072,7 +51071,7 @@
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>6</v>
       </c>
@@ -51083,7 +51082,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -51094,7 +51093,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -51105,7 +51104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22" s="11" t="s">
         <v>22</v>
@@ -51114,17 +51113,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>9</v>
       </c>
@@ -51133,7 +51132,7 @@
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
     </row>
-    <row r="27" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>6</v>
       </c>
@@ -51144,7 +51143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -51155,7 +51154,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>54</v>
       </c>
@@ -51164,7 +51163,7 @@
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>39</v>
       </c>
@@ -51181,7 +51180,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>1997</v>
       </c>
@@ -51194,7 +51193,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="20">
         <v>1998</v>
       </c>
@@ -51213,7 +51212,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>1999</v>
       </c>
@@ -51232,7 +51231,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>2000</v>
       </c>
@@ -51251,7 +51250,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>2001</v>
       </c>
@@ -51270,7 +51269,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="20">
         <v>2002</v>
       </c>
@@ -51289,7 +51288,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>2003</v>
       </c>
@@ -51308,7 +51307,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>2004</v>
       </c>
@@ -51327,7 +51326,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>2005</v>
       </c>
@@ -51346,7 +51345,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="20">
         <v>2006</v>
       </c>
@@ -51365,7 +51364,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25">
         <v>2007</v>
       </c>
@@ -51384,14 +51383,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -51399,7 +51398,7 @@
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -51408,13 +51407,13 @@
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="36" t="s">
         <v>44</v>
       </c>
@@ -51422,7 +51421,7 @@
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <f>1/A45</f>
         <v>17.22332068760786</v>
